--- a/OUTPUTS_CSV/Grade_Pronta_Noturno_SA.xlsx
+++ b/OUTPUTS_CSV/Grade_Pronta_Noturno_SA.xlsx
@@ -595,48 +595,70 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>[Quinzena I]
-Comunicações  Móveis  Opção Limitada
-(ESTI015-17 - SA)</t>
+Bioquímica
+(BCL0308-15 - SA)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fenômenos Eletromagnéticos
-(BCJ0203-15 - SA)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21:00-23:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Funções de Várias Variáveis
-(BCN0407-15 - SA)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
           <t>Introdução às Equações Diferenciais Ordinárias
 (BCN0405-15 - SA)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>[Quinzena I]
 Fenômenos Eletromagnéticos
 (BCJ0203-15 - SA)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[Quinzena I]
+Natureza da Informação
+(BCM0504-15 - SA)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>21:00-23:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fenômenos Eletromagnéticos
+(BCJ0203-15 - SA)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Natureza da Informação
+(BCM0504-15 - SA)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Geometria Analítica
+(BCN0404-15 - SA)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>[Quinzena I]
+Fenômenos Eletromagnéticos
+(BCJ0203-15 - SA)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bioquímica
+(BCL0308-15 - SA)</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="n"/>
     </row>
   </sheetData>
@@ -760,58 +782,68 @@
       <c r="B6" s="6" t="inlineStr">
         <is>
           <t>[Quinzena II]
-Comunicações  Móveis  Opção Limitada
-(ESTI015-17 - SA)</t>
+Física Quântica
+(BCK0103-15 - SA)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fenômenos Eletromagnéticos
-(BCJ0203-15 - SA)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>[Quinzena II]
-Bases Epistemológicas da Ciência Moderna
-(BIR0004-15 - SA)</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21:00-23:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Funções de Várias Variáveis
-(BCN0407-15 - SA)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
           <t>Introdução às Equações Diferenciais Ordinárias
 (BCN0405-15 - SA)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>[Quinzena II]
 Fenômenos Eletromagnéticos
 (BCJ0203-15 - SA)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>[Quinzena II]
-Bases Epistemológicas da Ciência Moderna
-(BIR0004-15 - SA)</t>
+Geometria Analítica
+(BCN0404-15 - SA)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>21:00-23:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fenômenos Eletromagnéticos
+(BCJ0203-15 - SA)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Natureza da Informação
+(BCM0504-15 - SA)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Geometria Analítica
+(BCN0404-15 - SA)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>[Quinzena II]
+Fenômenos Eletromagnéticos
+(BCJ0203-15 - SA)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bioquímica
+(BCL0308-15 - SA)</t>
         </is>
       </c>
       <c r="G7" s="3" t="n"/>
